--- a/data/ClueLayoutAdjTests.xlsx
+++ b/data/ClueLayoutAdjTests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\eclipse-workspace\C16A\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guske\eclipse-workspace\C16A\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1591AFE0-8D5B-4F5A-8487-64507B708CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DC9D2A-2B2B-4BC6-950F-CEF0244F3916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,12 +334,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
-        <bgColor rgb="FFD9D2E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF6AA84F"/>
       </patternFill>
@@ -365,12 +359,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor rgb="FF6AA84F"/>
       </patternFill>
     </fill>
@@ -384,6 +372,54 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF6AA84F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF6AA84F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -418,24 +454,29 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,35 +696,35 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" customWidth="1"/>
     <col min="9" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" customWidth="1"/>
-    <col min="14" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="6.28515625" customWidth="1"/>
-    <col min="17" max="17" width="5.42578125" customWidth="1"/>
-    <col min="18" max="18" width="5.85546875" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" customWidth="1"/>
-    <col min="20" max="20" width="7.42578125" customWidth="1"/>
-    <col min="21" max="21" width="6.42578125" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" customWidth="1"/>
-    <col min="27" max="27" width="47.42578125" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="14" max="15" width="7.109375" customWidth="1"/>
+    <col min="16" max="16" width="6.33203125" customWidth="1"/>
+    <col min="17" max="17" width="5.44140625" customWidth="1"/>
+    <col min="18" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" customWidth="1"/>
+    <col min="20" max="20" width="7.44140625" customWidth="1"/>
+    <col min="21" max="21" width="6.44140625" customWidth="1"/>
+    <col min="22" max="22" width="6.6640625" customWidth="1"/>
+    <col min="23" max="23" width="7.33203125" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" customWidth="1"/>
+    <col min="25" max="25" width="7.44140625" customWidth="1"/>
+    <col min="27" max="27" width="47.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <v>0</v>
       </c>
@@ -760,7 +801,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -782,7 +823,7 @@
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="30" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -836,11 +877,11 @@
       <c r="Y2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AA2" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -916,11 +957,11 @@
       <c r="Y3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA3" s="20" t="s">
+      <c r="AA3" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -957,7 +998,7 @@
       <c r="L4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="N4" s="5" t="s">
@@ -996,11 +1037,11 @@
       <c r="Y4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="AA4" s="20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1010,7 +1051,7 @@
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1076,11 +1117,11 @@
       <c r="Y5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA5" s="22" t="s">
+      <c r="AA5" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1156,11 +1197,11 @@
       <c r="Y6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA6" s="18" t="s">
+      <c r="AA6" s="34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1215,7 +1256,7 @@
       <c r="R7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="31" t="s">
+      <c r="S7" s="28" t="s">
         <v>11</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1236,11 +1277,11 @@
       <c r="Y7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AA7" s="23" t="s">
+      <c r="AA7" s="36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1262,7 +1303,7 @@
       <c r="G8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="22" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="4" t="s">
@@ -1289,7 +1330,7 @@
       <c r="P8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="32" t="s">
+      <c r="Q8" s="29" t="s">
         <v>3</v>
       </c>
       <c r="R8" s="4" t="s">
@@ -1317,7 +1358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1345,7 +1386,7 @@
       <c r="I9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="30" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="4" t="s">
@@ -1378,10 +1419,10 @@
       <c r="T9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="U9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="V9" s="35" t="s">
         <v>2</v>
       </c>
       <c r="W9" s="4" t="s">
@@ -1394,7 +1435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1404,13 +1445,13 @@
       <c r="C10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="25" t="s">
+      <c r="D10" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="23" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -1443,7 +1484,7 @@
       <c r="P10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="Q10" s="33" t="s">
+      <c r="Q10" s="30" t="s">
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
@@ -1471,11 +1512,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1548,7 +1589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1625,7 +1666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1662,7 +1703,7 @@
       <c r="L13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="26" t="s">
         <v>43</v>
       </c>
       <c r="N13" s="10" t="s">
@@ -1702,7 +1743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1733,19 +1774,19 @@
       <c r="J14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="23" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="40" t="s">
         <v>42</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="25" t="s">
+      <c r="O14" s="39" t="s">
         <v>12</v>
       </c>
       <c r="P14" s="4" t="s">
@@ -1779,14 +1820,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="12" t="s">
@@ -1795,7 +1836,7 @@
       <c r="E15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
@@ -1846,7 +1887,7 @@
       <c r="V15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="W15" s="7" t="s">
+      <c r="W15" s="38" t="s">
         <v>22</v>
       </c>
       <c r="X15" s="11" t="s">
@@ -1856,7 +1897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1884,10 +1925,10 @@
       <c r="I16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="K16" s="33" t="s">
+      <c r="J16" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>2</v>
       </c>
       <c r="L16" s="10" t="s">
@@ -1933,7 +1974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2010,7 +2051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2087,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2164,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2192,7 +2233,7 @@
       <c r="I20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J20" s="26" t="s">
+      <c r="J20" s="24" t="s">
         <v>2</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -2201,7 +2242,7 @@
       <c r="L20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M20" s="25" t="s">
+      <c r="M20" s="23" t="s">
         <v>23</v>
       </c>
       <c r="N20" s="4" t="s">
@@ -2219,13 +2260,13 @@
       <c r="R20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="S20" s="33" t="s">
+      <c r="S20" s="30" t="s">
         <v>2</v>
       </c>
       <c r="T20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="U20" s="25" t="s">
+      <c r="U20" s="23" t="s">
         <v>23</v>
       </c>
       <c r="V20" s="4" t="s">
@@ -2237,11 +2278,11 @@
       <c r="X20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="Y20" s="33" t="s">
+      <c r="Y20" s="30" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2318,7 +2359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2340,7 +2381,7 @@
       <c r="G22" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="27" t="s">
         <v>12</v>
       </c>
       <c r="I22" s="4" t="s">
@@ -2395,7 +2436,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2472,7 +2513,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2482,7 +2523,7 @@
       <c r="C24" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="38" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="14" t="s">
@@ -2509,7 +2550,7 @@
       <c r="L24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="M24" s="27" t="s">
+      <c r="M24" s="25" t="s">
         <v>32</v>
       </c>
       <c r="N24" s="15" t="s">
@@ -2549,7 +2590,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2601,7 +2642,7 @@
       <c r="Q25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="4" t="s">
+      <c r="R25" s="35" t="s">
         <v>2</v>
       </c>
       <c r="S25" s="4" t="s">
@@ -2626,7 +2667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2703,7 +2744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2728,7 +2769,7 @@
       <c r="H27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="31" t="s">
         <v>2</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -2755,7 +2796,7 @@
       <c r="Q27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="R27" s="37" t="s">
         <v>2</v>
       </c>
       <c r="S27" s="3" t="s">
@@ -2780,7 +2821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
       <c r="I28" s="1"/>
     </row>
   </sheetData>

--- a/data/ClueLayoutAdjTests.xlsx
+++ b/data/ClueLayoutAdjTests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\eclipse-workspace\C16A\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1591AFE0-8D5B-4F5A-8487-64507B708CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22970BCD-0521-4629-8FED-985FE00B3C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1650" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
